--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Март 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Март 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92556535123</v>
+        <v>46157.93117344684</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Март 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Март 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93117344684</v>
+        <v>46157.93139526119</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Март 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Март 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93139526119</v>
+        <v>46157.93386332706</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Март 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Март 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93386332706</v>
+        <v>46157.93698059452</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Март 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Март 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93698059452</v>
+        <v>46158.28206111817</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Март 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Март 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28206111817</v>
+        <v>46158.29655008538</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Март 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Март 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29655008538</v>
+        <v>46158.29810117956</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Март 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Март 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29810117956</v>
+        <v>46158.33372414431</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Март 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Март 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33372414431</v>
+        <v>46158.37224760495</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Март 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Март 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37224760495</v>
+        <v>46158.37276702015</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
